--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\ReactProjects\Predicting-Cinema-Hall-Revenue\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -600,7 +600,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns="" r:embed="rId2"/>
+              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -650,7 +650,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns="" r:embed="rId4"/>
+              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -1682,7 +1682,7 @@
         <v>45747</v>
       </c>
       <c r="E21" s="13">
-        <v>45752</v>
+        <v>45766</v>
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="11"/>
@@ -1713,7 +1713,7 @@
         <v>45747</v>
       </c>
       <c r="E22" s="13">
-        <v>45752</v>
+        <v>45766</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="11"/>
@@ -1744,7 +1744,7 @@
         <v>45747</v>
       </c>
       <c r="E23" s="13">
-        <v>45752</v>
+        <v>45766</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="11"/>
@@ -1775,7 +1775,7 @@
         <v>45747</v>
       </c>
       <c r="E24" s="13">
-        <v>45752</v>
+        <v>45766</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="11"/>
@@ -1806,7 +1806,7 @@
         <v>45747</v>
       </c>
       <c r="E25" s="13">
-        <v>45752</v>
+        <v>45766</v>
       </c>
       <c r="F25" s="15"/>
       <c r="G25" s="11"/>
@@ -1859,10 +1859,10 @@
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="13">
-        <v>45754</v>
+        <v>45767</v>
       </c>
       <c r="E27" s="13">
-        <v>45758</v>
+        <v>45779</v>
       </c>
       <c r="F27" s="14"/>
       <c r="G27" s="11"/>
@@ -1890,10 +1890,10 @@
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="13">
-        <v>45754</v>
+        <v>45767</v>
       </c>
       <c r="E28" s="13">
-        <v>45758</v>
+        <v>45779</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="11"/>
@@ -1921,10 +1921,10 @@
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="13">
-        <v>45754</v>
+        <v>45767</v>
       </c>
       <c r="E29" s="13">
-        <v>45758</v>
+        <v>45779</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="11"/>
@@ -1952,10 +1952,10 @@
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="13">
-        <v>45754</v>
+        <v>45767</v>
       </c>
       <c r="E30" s="13">
-        <v>45758</v>
+        <v>45779</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="11"/>
